--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/18 12:26:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>31055</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31055.9</t>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31055.9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>31055</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>31055.9</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31055.9</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>49460.81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>31055</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.9</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18405.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>400000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>49460.81</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>49460.81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>36055</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18405.81</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13405.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>400000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>49460.81</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>49460.81</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>49459</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>13405.81</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,166 +117,181 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -298,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>400000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>49460.81</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>61582.02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>49459</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.81</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12123.02</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,83 +340,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>61582.02</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>61582.02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>49847</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>12123.02</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11735.02</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,12 +340,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -367,83 +367,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>61582.02</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>49847</t>
+          <t>61582.02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>61580</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>11735.02</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.02</t>
         </is>
       </c>
     </row>
